--- a/data/judo_therapy/data.xlsx
+++ b/data/judo_therapy/data.xlsx
@@ -2004,10 +2004,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>末沢接骨院</v>
+        <v>末澤接骨院</v>
       </c>
       <c r="C51" t="str">
-        <v>末沢　彰一</v>
+        <v>末澤　彰一</v>
       </c>
       <c r="D51" t="str">
         <v>34.293765</v>
@@ -4800,7 +4800,7 @@
         <v>134.07861</v>
       </c>
       <c r="F138" t="str">
-        <v>香川県高松市木太町３５０５－１</v>
+        <v>香川県高松市木太町３５０５−１</v>
       </c>
       <c r="G138" t="str">
         <v>087-861-9112</v>
@@ -6752,7 +6752,7 @@
         <v>134.07269</v>
       </c>
       <c r="F199" t="str">
-        <v>高松市福岡町３－８－５　イオン高松東店２Ｆ</v>
+        <v>高松市福岡町３−８−５　イオン高松東店２Ｆ</v>
       </c>
       <c r="G199" t="str">
         <v>087-811-7022</v>

--- a/data/judo_therapy/data.xlsx
+++ b/data/judo_therapy/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ivpf201v.takamatsu.local\Profile\52845\Documents\Downloads\オープンデータ\4月\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\userdata\52845\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72F26E8C-464E-4600-85A2-3DC8368B6811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBEBFE9-3B3B-42E7-A624-32BA5D5613E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="1351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="1358">
   <si>
     <t>№</t>
   </si>
@@ -460,7 +460,7 @@
     <t>134.04817</t>
   </si>
   <si>
-    <t>高松市太田下町１７７２－３</t>
+    <t>高松市太田下町１７７２−３</t>
   </si>
   <si>
     <t>1993/04/01</t>
@@ -4073,6 +4073,27 @@
   </si>
   <si>
     <t>2025/12/10</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>ＭＴＳＢ接骨院</t>
+  </si>
+  <si>
+    <t>中井　幹雄</t>
+  </si>
+  <si>
+    <t>34.317849</t>
+  </si>
+  <si>
+    <t>134.057796</t>
+  </si>
+  <si>
+    <t>高松市松縄町１０４９番地１４　フィーレ松縄F棟</t>
+  </si>
+  <si>
+    <t>2026/5/30</t>
   </si>
 </sst>
 </file>
@@ -4456,10 +4477,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I198"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I199"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4488,7 +4509,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4517,7 +4538,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -4546,7 +4567,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -4575,7 +4596,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -4604,7 +4625,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -4633,7 +4654,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -4662,7 +4683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>50</v>
       </c>
@@ -4691,7 +4712,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>57</v>
       </c>
@@ -4720,7 +4741,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>64</v>
       </c>
@@ -4749,7 +4770,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>71</v>
       </c>
@@ -4778,7 +4799,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>78</v>
       </c>
@@ -4807,7 +4828,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>85</v>
       </c>
@@ -4836,7 +4857,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>92</v>
       </c>
@@ -4865,7 +4886,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>99</v>
       </c>
@@ -4894,7 +4915,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>106</v>
       </c>
@@ -4923,7 +4944,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>113</v>
       </c>
@@ -4952,7 +4973,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>120</v>
       </c>
@@ -4981,7 +5002,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>127</v>
       </c>
@@ -5010,7 +5031,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>134</v>
       </c>
@@ -5039,7 +5060,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>141</v>
       </c>
@@ -5068,7 +5089,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>148</v>
       </c>
@@ -5097,7 +5118,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>155</v>
       </c>
@@ -5126,7 +5147,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>162</v>
       </c>
@@ -5155,7 +5176,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>169</v>
       </c>
@@ -5184,7 +5205,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>176</v>
       </c>
@@ -5213,7 +5234,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>183</v>
       </c>
@@ -5242,7 +5263,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>190</v>
       </c>
@@ -5271,7 +5292,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>197</v>
       </c>
@@ -5300,7 +5321,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>204</v>
       </c>
@@ -5329,7 +5350,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>211</v>
       </c>
@@ -5358,7 +5379,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>218</v>
       </c>
@@ -5387,7 +5408,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>225</v>
       </c>
@@ -5416,7 +5437,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>232</v>
       </c>
@@ -5445,7 +5466,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>239</v>
       </c>
@@ -5474,7 +5495,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>246</v>
       </c>
@@ -5503,7 +5524,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>253</v>
       </c>
@@ -5532,7 +5553,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>260</v>
       </c>
@@ -5561,7 +5582,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>267</v>
       </c>
@@ -5590,7 +5611,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>274</v>
       </c>
@@ -5619,7 +5640,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>281</v>
       </c>
@@ -5648,7 +5669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>288</v>
       </c>
@@ -5677,7 +5698,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>295</v>
       </c>
@@ -5706,7 +5727,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>302</v>
       </c>
@@ -5735,7 +5756,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>309</v>
       </c>
@@ -5764,7 +5785,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>316</v>
       </c>
@@ -5793,7 +5814,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>323</v>
       </c>
@@ -5822,7 +5843,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>330</v>
       </c>
@@ -5851,7 +5872,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>337</v>
       </c>
@@ -5880,7 +5901,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>344</v>
       </c>
@@ -5909,7 +5930,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>351</v>
       </c>
@@ -5938,7 +5959,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>358</v>
       </c>
@@ -5967,7 +5988,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>365</v>
       </c>
@@ -5996,7 +6017,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>371</v>
       </c>
@@ -6025,7 +6046,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>378</v>
       </c>
@@ -6054,7 +6075,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>385</v>
       </c>
@@ -6083,7 +6104,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>392</v>
       </c>
@@ -6112,7 +6133,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>399</v>
       </c>
@@ -6141,7 +6162,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>406</v>
       </c>
@@ -6170,7 +6191,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>412</v>
       </c>
@@ -6199,7 +6220,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>419</v>
       </c>
@@ -6228,7 +6249,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>426</v>
       </c>
@@ -6257,7 +6278,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>433</v>
       </c>
@@ -6286,7 +6307,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>440</v>
       </c>
@@ -6315,7 +6336,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>447</v>
       </c>
@@ -6344,7 +6365,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>454</v>
       </c>
@@ -6373,7 +6394,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>461</v>
       </c>
@@ -6402,7 +6423,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>468</v>
       </c>
@@ -6431,7 +6452,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>475</v>
       </c>
@@ -6460,7 +6481,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>482</v>
       </c>
@@ -6489,7 +6510,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>489</v>
       </c>
@@ -6518,7 +6539,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>496</v>
       </c>
@@ -6547,7 +6568,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>503</v>
       </c>
@@ -6576,7 +6597,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>510</v>
       </c>
@@ -6605,7 +6626,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>517</v>
       </c>
@@ -6634,7 +6655,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>524</v>
       </c>
@@ -6663,7 +6684,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>531</v>
       </c>
@@ -6692,7 +6713,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>538</v>
       </c>
@@ -6721,7 +6742,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>545</v>
       </c>
@@ -6750,7 +6771,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>552</v>
       </c>
@@ -6779,7 +6800,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>559</v>
       </c>
@@ -6808,7 +6829,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>566</v>
       </c>
@@ -6837,7 +6858,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>573</v>
       </c>
@@ -6866,7 +6887,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>580</v>
       </c>
@@ -6895,7 +6916,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>587</v>
       </c>
@@ -6924,7 +6945,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>594</v>
       </c>
@@ -6953,7 +6974,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>601</v>
       </c>
@@ -6982,7 +7003,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>608</v>
       </c>
@@ -7011,7 +7032,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>615</v>
       </c>
@@ -7040,7 +7061,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>622</v>
       </c>
@@ -7069,7 +7090,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>629</v>
       </c>
@@ -7098,7 +7119,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>636</v>
       </c>
@@ -7127,7 +7148,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>640</v>
       </c>
@@ -7156,7 +7177,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>647</v>
       </c>
@@ -7185,7 +7206,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>654</v>
       </c>
@@ -7214,7 +7235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>661</v>
       </c>
@@ -7243,7 +7264,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>668</v>
       </c>
@@ -7272,7 +7293,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>674</v>
       </c>
@@ -7301,7 +7322,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>681</v>
       </c>
@@ -7330,7 +7351,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>688</v>
       </c>
@@ -7359,7 +7380,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>694</v>
       </c>
@@ -7388,7 +7409,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>701</v>
       </c>
@@ -7417,7 +7438,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>708</v>
       </c>
@@ -7446,7 +7467,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>715</v>
       </c>
@@ -7475,7 +7496,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>722</v>
       </c>
@@ -7504,7 +7525,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>729</v>
       </c>
@@ -7533,7 +7554,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>736</v>
       </c>
@@ -7562,7 +7583,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>743</v>
       </c>
@@ -7591,7 +7612,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>750</v>
       </c>
@@ -7620,7 +7641,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>757</v>
       </c>
@@ -7649,7 +7670,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>764</v>
       </c>
@@ -7678,7 +7699,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>770</v>
       </c>
@@ -7707,7 +7728,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>777</v>
       </c>
@@ -7736,7 +7757,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>784</v>
       </c>
@@ -7765,7 +7786,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>791</v>
       </c>
@@ -7794,7 +7815,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>798</v>
       </c>
@@ -7823,7 +7844,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>805</v>
       </c>
@@ -7852,7 +7873,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>812</v>
       </c>
@@ -7881,7 +7902,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>819</v>
       </c>
@@ -7910,7 +7931,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>826</v>
       </c>
@@ -7939,7 +7960,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>833</v>
       </c>
@@ -7968,7 +7989,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>840</v>
       </c>
@@ -7997,7 +8018,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>847</v>
       </c>
@@ -8026,7 +8047,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>854</v>
       </c>
@@ -8055,7 +8076,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>861</v>
       </c>
@@ -8084,7 +8105,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>868</v>
       </c>
@@ -8113,7 +8134,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>875</v>
       </c>
@@ -8142,7 +8163,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>882</v>
       </c>
@@ -8171,7 +8192,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>889</v>
       </c>
@@ -8200,7 +8221,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>896</v>
       </c>
@@ -8229,7 +8250,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>902</v>
       </c>
@@ -8258,7 +8279,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>906</v>
       </c>
@@ -8287,7 +8308,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>911</v>
       </c>
@@ -8316,7 +8337,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>916</v>
       </c>
@@ -8345,7 +8366,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>923</v>
       </c>
@@ -8374,7 +8395,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>929</v>
       </c>
@@ -8403,7 +8424,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>936</v>
       </c>
@@ -8432,7 +8453,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>943</v>
       </c>
@@ -8461,7 +8482,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>949</v>
       </c>
@@ -8490,7 +8511,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>955</v>
       </c>
@@ -8519,7 +8540,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>961</v>
       </c>
@@ -8548,7 +8569,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>968</v>
       </c>
@@ -8577,7 +8598,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>975</v>
       </c>
@@ -8606,7 +8627,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>982</v>
       </c>
@@ -8635,7 +8656,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>986</v>
       </c>
@@ -8664,7 +8685,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>993</v>
       </c>
@@ -8693,7 +8714,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>1000</v>
       </c>
@@ -8722,7 +8743,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>1007</v>
       </c>
@@ -8751,7 +8772,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>1014</v>
       </c>
@@ -8780,7 +8801,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>1021</v>
       </c>
@@ -8809,7 +8830,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>1028</v>
       </c>
@@ -8838,7 +8859,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>1035</v>
       </c>
@@ -8867,7 +8888,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>1042</v>
       </c>
@@ -8896,7 +8917,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>1048</v>
       </c>
@@ -8925,7 +8946,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>1055</v>
       </c>
@@ -8954,7 +8975,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>1062</v>
       </c>
@@ -8983,7 +9004,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>1069</v>
       </c>
@@ -9012,7 +9033,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>1076</v>
       </c>
@@ -9041,7 +9062,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>1083</v>
       </c>
@@ -9070,7 +9091,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>1090</v>
       </c>
@@ -9099,143 +9120,140 @@
         <v>15</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B161" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C161" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D161" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E161" t="s">
+        <v>1355</v>
+      </c>
+      <c r="F161" t="s">
+        <v>1356</v>
+      </c>
+      <c r="G161" t="s">
+        <v>1357</v>
+      </c>
+      <c r="I161" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
         <v>1097</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B162" t="s">
         <v>1098</v>
       </c>
-      <c r="C161" t="s">
+      <c r="C162" t="s">
         <v>1099</v>
       </c>
-      <c r="D161" t="s">
+      <c r="D162" t="s">
         <v>1100</v>
       </c>
-      <c r="E161" t="s">
+      <c r="E162" t="s">
         <v>1101</v>
       </c>
-      <c r="F161" t="s">
+      <c r="F162" t="s">
         <v>1102</v>
       </c>
-      <c r="G161" t="s">
+      <c r="G162" t="s">
         <v>1103</v>
       </c>
-      <c r="H161" t="s">
-        <v>15</v>
-      </c>
-      <c r="I161" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A162" t="s">
+      <c r="H162" t="s">
+        <v>15</v>
+      </c>
+      <c r="I162" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
         <v>1104</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B163" t="s">
         <v>1105</v>
       </c>
-      <c r="C162" t="s">
+      <c r="C163" t="s">
         <v>1106</v>
       </c>
-      <c r="D162" t="s">
+      <c r="D163" t="s">
         <v>1107</v>
       </c>
-      <c r="E162" t="s">
+      <c r="E163" t="s">
         <v>1108</v>
       </c>
-      <c r="F162" t="s">
+      <c r="F163" t="s">
         <v>1109</v>
       </c>
-      <c r="G162" t="s">
+      <c r="G163" t="s">
         <v>1110</v>
       </c>
-      <c r="H162" t="s">
+      <c r="H163" t="s">
         <v>16</v>
       </c>
-      <c r="I162" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A163" t="s">
+      <c r="I163" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
         <v>1111</v>
       </c>
-      <c r="B163" t="s">
+      <c r="B164" t="s">
         <v>1112</v>
       </c>
-      <c r="C163" t="s">
+      <c r="C164" t="s">
         <v>1113</v>
       </c>
-      <c r="D163" t="s">
+      <c r="D164" t="s">
         <v>1114</v>
       </c>
-      <c r="E163" t="s">
+      <c r="E164" t="s">
         <v>1115</v>
       </c>
-      <c r="F163" t="s">
+      <c r="F164" t="s">
         <v>1116</v>
       </c>
-      <c r="G163" t="s">
+      <c r="G164" t="s">
         <v>1117</v>
       </c>
-      <c r="H163" t="s">
-        <v>15</v>
-      </c>
-      <c r="I163" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A164" t="s">
+      <c r="H164" t="s">
+        <v>15</v>
+      </c>
+      <c r="I164" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
         <v>1118</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B165" t="s">
         <v>1119</v>
       </c>
-      <c r="C164" t="s">
+      <c r="C165" t="s">
         <v>1120</v>
       </c>
-      <c r="D164" t="s">
+      <c r="D165" t="s">
         <v>1121</v>
       </c>
-      <c r="E164" t="s">
+      <c r="E165" t="s">
         <v>1122</v>
       </c>
-      <c r="F164" t="s">
+      <c r="F165" t="s">
         <v>1123</v>
       </c>
-      <c r="G164" t="s">
+      <c r="G165" t="s">
         <v>1124</v>
-      </c>
-      <c r="H164" t="s">
-        <v>16</v>
-      </c>
-      <c r="I164" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A165" t="s">
-        <v>1125</v>
-      </c>
-      <c r="B165" t="s">
-        <v>1126</v>
-      </c>
-      <c r="C165" t="s">
-        <v>1127</v>
-      </c>
-      <c r="D165" t="s">
-        <v>1128</v>
-      </c>
-      <c r="E165" t="s">
-        <v>1129</v>
-      </c>
-      <c r="F165" t="s">
-        <v>1130</v>
-      </c>
-      <c r="G165" t="s">
-        <v>1131</v>
       </c>
       <c r="H165" t="s">
         <v>16</v>
@@ -9244,27 +9262,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>1132</v>
+        <v>1125</v>
       </c>
       <c r="B166" t="s">
-        <v>100</v>
+        <v>1126</v>
       </c>
       <c r="C166" t="s">
-        <v>1133</v>
+        <v>1127</v>
       </c>
       <c r="D166" t="s">
-        <v>102</v>
+        <v>1128</v>
       </c>
       <c r="E166" t="s">
-        <v>103</v>
+        <v>1129</v>
       </c>
       <c r="F166" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="G166" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="H166" t="s">
         <v>16</v>
@@ -9273,27 +9291,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="B167" t="s">
-        <v>1137</v>
+        <v>100</v>
       </c>
       <c r="C167" t="s">
-        <v>1138</v>
+        <v>1133</v>
       </c>
       <c r="D167" t="s">
-        <v>1139</v>
+        <v>102</v>
       </c>
       <c r="E167" t="s">
-        <v>1140</v>
+        <v>103</v>
       </c>
       <c r="F167" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
       <c r="G167" t="s">
-        <v>1142</v>
+        <v>1135</v>
       </c>
       <c r="H167" t="s">
         <v>16</v>
@@ -9302,85 +9320,85 @@
         <v>15</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B168" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C168" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D168" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E168" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F168" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G168" t="s">
+        <v>1142</v>
+      </c>
+      <c r="H168" t="s">
+        <v>16</v>
+      </c>
+      <c r="I168" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
         <v>1143</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B169" t="s">
         <v>1144</v>
       </c>
-      <c r="C168" t="s">
+      <c r="C169" t="s">
         <v>1145</v>
       </c>
-      <c r="D168" t="s">
+      <c r="D169" t="s">
         <v>1146</v>
       </c>
-      <c r="E168" t="s">
+      <c r="E169" t="s">
         <v>1147</v>
       </c>
-      <c r="F168" t="s">
+      <c r="F169" t="s">
         <v>1148</v>
       </c>
-      <c r="G168" t="s">
+      <c r="G169" t="s">
         <v>1149</v>
       </c>
-      <c r="H168" t="s">
-        <v>15</v>
-      </c>
-      <c r="I168" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A169" t="s">
+      <c r="H169" t="s">
+        <v>15</v>
+      </c>
+      <c r="I169" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A170" t="s">
         <v>1150</v>
       </c>
-      <c r="B169" t="s">
+      <c r="B170" t="s">
         <v>1151</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C170" t="s">
         <v>1152</v>
       </c>
-      <c r="D169" t="s">
+      <c r="D170" t="s">
         <v>1153</v>
       </c>
-      <c r="E169" t="s">
+      <c r="E170" t="s">
         <v>1154</v>
       </c>
-      <c r="F169" t="s">
+      <c r="F170" t="s">
         <v>1155</v>
       </c>
-      <c r="G169" t="s">
+      <c r="G170" t="s">
         <v>1156</v>
-      </c>
-      <c r="H169" t="s">
-        <v>16</v>
-      </c>
-      <c r="I169" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A170" t="s">
-        <v>1157</v>
-      </c>
-      <c r="B170" t="s">
-        <v>1158</v>
-      </c>
-      <c r="C170" t="s">
-        <v>1159</v>
-      </c>
-      <c r="D170" t="s">
-        <v>1160</v>
-      </c>
-      <c r="E170" t="s">
-        <v>1161</v>
-      </c>
-      <c r="F170" t="s">
-        <v>1162</v>
-      </c>
-      <c r="G170" t="s">
-        <v>1163</v>
       </c>
       <c r="H170" t="s">
         <v>16</v>
@@ -9389,27 +9407,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>1164</v>
+        <v>1157</v>
       </c>
       <c r="B171" t="s">
-        <v>1165</v>
+        <v>1158</v>
       </c>
       <c r="C171" t="s">
-        <v>1166</v>
+        <v>1159</v>
       </c>
       <c r="D171" t="s">
-        <v>1167</v>
+        <v>1160</v>
       </c>
       <c r="E171" t="s">
-        <v>1168</v>
+        <v>1161</v>
       </c>
       <c r="F171" t="s">
-        <v>1169</v>
+        <v>1162</v>
       </c>
       <c r="G171" t="s">
-        <v>1170</v>
+        <v>1163</v>
       </c>
       <c r="H171" t="s">
         <v>16</v>
@@ -9418,172 +9436,172 @@
         <v>15</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B172" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C172" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D172" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E172" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F172" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G172" t="s">
+        <v>1170</v>
+      </c>
+      <c r="H172" t="s">
+        <v>16</v>
+      </c>
+      <c r="I172" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A173" t="s">
         <v>1171</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B173" t="s">
         <v>1172</v>
       </c>
-      <c r="C172" t="s">
+      <c r="C173" t="s">
         <v>1173</v>
       </c>
-      <c r="D172" t="s">
+      <c r="D173" t="s">
         <v>1174</v>
       </c>
-      <c r="E172" t="s">
+      <c r="E173" t="s">
         <v>1175</v>
       </c>
-      <c r="F172" t="s">
+      <c r="F173" t="s">
         <v>1176</v>
       </c>
-      <c r="G172" t="s">
+      <c r="G173" t="s">
         <v>1177</v>
       </c>
-      <c r="H172" t="s">
-        <v>15</v>
-      </c>
-      <c r="I172" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A173" t="s">
+      <c r="H173" t="s">
+        <v>15</v>
+      </c>
+      <c r="I173" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
         <v>1178</v>
       </c>
-      <c r="B173" t="s">
+      <c r="B174" t="s">
         <v>1179</v>
       </c>
-      <c r="C173" t="s">
+      <c r="C174" t="s">
         <v>1180</v>
       </c>
-      <c r="D173" t="s">
+      <c r="D174" t="s">
         <v>1181</v>
       </c>
-      <c r="E173" t="s">
+      <c r="E174" t="s">
         <v>1182</v>
       </c>
-      <c r="F173" t="s">
+      <c r="F174" t="s">
         <v>1183</v>
       </c>
-      <c r="G173" t="s">
+      <c r="G174" t="s">
         <v>1184</v>
       </c>
-      <c r="H173" t="s">
-        <v>15</v>
-      </c>
-      <c r="I173" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A174" t="s">
+      <c r="H174" t="s">
+        <v>15</v>
+      </c>
+      <c r="I174" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
         <v>1185</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B175" t="s">
         <v>1186</v>
       </c>
-      <c r="C174" t="s">
+      <c r="C175" t="s">
         <v>1187</v>
       </c>
-      <c r="D174" t="s">
+      <c r="D175" t="s">
         <v>1188</v>
       </c>
-      <c r="E174" t="s">
+      <c r="E175" t="s">
         <v>1189</v>
       </c>
-      <c r="F174" t="s">
+      <c r="F175" t="s">
         <v>1190</v>
       </c>
-      <c r="G174" t="s">
+      <c r="G175" t="s">
         <v>1191</v>
       </c>
-      <c r="H174" t="s">
-        <v>15</v>
-      </c>
-      <c r="I174" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A175" t="s">
+      <c r="H175" t="s">
+        <v>15</v>
+      </c>
+      <c r="I175" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A176" t="s">
         <v>1192</v>
       </c>
-      <c r="B175" t="s">
+      <c r="B176" t="s">
         <v>1193</v>
       </c>
-      <c r="C175" t="s">
+      <c r="C176" t="s">
         <v>1194</v>
       </c>
-      <c r="D175" t="s">
+      <c r="D176" t="s">
         <v>1195</v>
       </c>
-      <c r="E175" t="s">
+      <c r="E176" t="s">
         <v>1196</v>
       </c>
-      <c r="F175" t="s">
+      <c r="F176" t="s">
         <v>1197</v>
-      </c>
-      <c r="G175" t="s">
-        <v>1184</v>
-      </c>
-      <c r="H175" t="s">
-        <v>15</v>
-      </c>
-      <c r="I175" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A176" t="s">
-        <v>1198</v>
-      </c>
-      <c r="B176" t="s">
-        <v>1199</v>
-      </c>
-      <c r="C176" t="s">
-        <v>1200</v>
-      </c>
-      <c r="D176" t="s">
-        <v>1201</v>
-      </c>
-      <c r="E176" t="s">
-        <v>1202</v>
-      </c>
-      <c r="F176" t="s">
-        <v>1203</v>
       </c>
       <c r="G176" t="s">
         <v>1184</v>
       </c>
       <c r="H176" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I176" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>1204</v>
+        <v>1198</v>
       </c>
       <c r="B177" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="C177" t="s">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="D177" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="E177" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="F177" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="G177" t="s">
-        <v>1210</v>
+        <v>1184</v>
       </c>
       <c r="H177" t="s">
         <v>16</v>
@@ -9592,346 +9610,346 @@
         <v>15</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B178" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C178" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D178" t="s">
+        <v>1207</v>
+      </c>
+      <c r="E178" t="s">
+        <v>1208</v>
+      </c>
+      <c r="F178" t="s">
+        <v>1209</v>
+      </c>
+      <c r="G178" t="s">
+        <v>1210</v>
+      </c>
+      <c r="H178" t="s">
+        <v>16</v>
+      </c>
+      <c r="I178" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A179" t="s">
         <v>1211</v>
       </c>
-      <c r="B178" t="s">
+      <c r="B179" t="s">
         <v>1212</v>
       </c>
-      <c r="C178" t="s">
+      <c r="C179" t="s">
         <v>1213</v>
       </c>
-      <c r="D178" t="s">
+      <c r="D179" t="s">
         <v>1214</v>
       </c>
-      <c r="E178" t="s">
+      <c r="E179" t="s">
         <v>1215</v>
       </c>
-      <c r="F178" t="s">
+      <c r="F179" t="s">
         <v>1216</v>
       </c>
-      <c r="G178" t="s">
+      <c r="G179" t="s">
         <v>1217</v>
       </c>
-      <c r="H178" t="s">
-        <v>15</v>
-      </c>
-      <c r="I178" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A179" t="s">
+      <c r="H179" t="s">
+        <v>15</v>
+      </c>
+      <c r="I179" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
         <v>1218</v>
       </c>
-      <c r="B179" t="s">
+      <c r="B180" t="s">
         <v>1219</v>
       </c>
-      <c r="C179" t="s">
+      <c r="C180" t="s">
         <v>1220</v>
       </c>
-      <c r="D179" t="s">
+      <c r="D180" t="s">
         <v>1221</v>
       </c>
-      <c r="E179" t="s">
+      <c r="E180" t="s">
         <v>1222</v>
       </c>
-      <c r="F179" t="s">
+      <c r="F180" t="s">
         <v>1223</v>
       </c>
-      <c r="G179" t="s">
+      <c r="G180" t="s">
         <v>1096</v>
       </c>
-      <c r="H179" t="s">
-        <v>15</v>
-      </c>
-      <c r="I179" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A180" t="s">
+      <c r="H180" t="s">
+        <v>15</v>
+      </c>
+      <c r="I180" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A181" t="s">
         <v>1224</v>
       </c>
-      <c r="B180" t="s">
+      <c r="B181" t="s">
         <v>1225</v>
       </c>
-      <c r="C180" t="s">
+      <c r="C181" t="s">
         <v>1226</v>
       </c>
-      <c r="D180" t="s">
+      <c r="D181" t="s">
         <v>1227</v>
       </c>
-      <c r="E180" t="s">
+      <c r="E181" t="s">
         <v>1228</v>
       </c>
-      <c r="F180" t="s">
+      <c r="F181" t="s">
         <v>1229</v>
       </c>
-      <c r="G180" t="s">
+      <c r="G181" t="s">
         <v>1230</v>
       </c>
-      <c r="H180" t="s">
-        <v>15</v>
-      </c>
-      <c r="I180" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A181" t="s">
+      <c r="H181" t="s">
+        <v>15</v>
+      </c>
+      <c r="I181" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A182" t="s">
         <v>1231</v>
       </c>
-      <c r="B181" t="s">
+      <c r="B182" t="s">
         <v>1232</v>
       </c>
-      <c r="C181" t="s">
+      <c r="C182" t="s">
         <v>1233</v>
       </c>
-      <c r="D181" t="s">
+      <c r="D182" t="s">
         <v>33</v>
       </c>
-      <c r="E181" t="s">
+      <c r="E182" t="s">
         <v>1234</v>
       </c>
-      <c r="F181" t="s">
+      <c r="F182" t="s">
         <v>1235</v>
       </c>
-      <c r="G181" t="s">
+      <c r="G182" t="s">
         <v>1236</v>
       </c>
-      <c r="H181" t="s">
-        <v>15</v>
-      </c>
-      <c r="I181" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A182" t="s">
+      <c r="H182" t="s">
+        <v>15</v>
+      </c>
+      <c r="I182" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
         <v>1237</v>
       </c>
-      <c r="B182" t="s">
+      <c r="B183" t="s">
         <v>1238</v>
       </c>
-      <c r="C182" t="s">
+      <c r="C183" t="s">
         <v>1239</v>
       </c>
-      <c r="D182" t="s">
+      <c r="D183" t="s">
         <v>1240</v>
       </c>
-      <c r="E182" t="s">
+      <c r="E183" t="s">
         <v>1241</v>
       </c>
-      <c r="F182" t="s">
+      <c r="F183" t="s">
         <v>1242</v>
       </c>
-      <c r="G182" t="s">
+      <c r="G183" t="s">
         <v>1243</v>
       </c>
-      <c r="H182" t="s">
-        <v>15</v>
-      </c>
-      <c r="I182" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A183" t="s">
+      <c r="H183" t="s">
+        <v>15</v>
+      </c>
+      <c r="I183" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
         <v>1244</v>
       </c>
-      <c r="B183" t="s">
+      <c r="B184" t="s">
         <v>1245</v>
       </c>
-      <c r="C183" t="s">
+      <c r="C184" t="s">
         <v>1246</v>
       </c>
-      <c r="D183" t="s">
+      <c r="D184" t="s">
         <v>1247</v>
       </c>
-      <c r="E183" t="s">
+      <c r="E184" t="s">
         <v>1248</v>
       </c>
-      <c r="F183" t="s">
+      <c r="F184" t="s">
         <v>1249</v>
       </c>
-      <c r="G183" t="s">
+      <c r="G184" t="s">
         <v>1250</v>
       </c>
-      <c r="H183" t="s">
+      <c r="H184" t="s">
         <v>16</v>
       </c>
-      <c r="I183" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A184" t="s">
+      <c r="I184" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A185" t="s">
         <v>1251</v>
       </c>
-      <c r="B184" t="s">
+      <c r="B185" t="s">
         <v>1252</v>
       </c>
-      <c r="C184" t="s">
+      <c r="C185" t="s">
         <v>1253</v>
       </c>
-      <c r="D184" t="s">
+      <c r="D185" t="s">
         <v>1254</v>
       </c>
-      <c r="E184" t="s">
+      <c r="E185" t="s">
         <v>1255</v>
       </c>
-      <c r="F184" t="s">
+      <c r="F185" t="s">
         <v>1256</v>
       </c>
-      <c r="G184" t="s">
+      <c r="G185" t="s">
         <v>1257</v>
       </c>
-      <c r="H184" t="s">
-        <v>15</v>
-      </c>
-      <c r="I184" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A185" t="s">
+      <c r="H185" t="s">
+        <v>15</v>
+      </c>
+      <c r="I185" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A186" t="s">
         <v>1258</v>
       </c>
-      <c r="B185" t="s">
+      <c r="B186" t="s">
         <v>1259</v>
       </c>
-      <c r="C185" t="s">
+      <c r="C186" t="s">
         <v>1260</v>
       </c>
-      <c r="D185" t="s">
+      <c r="D186" t="s">
         <v>1261</v>
       </c>
-      <c r="E185" t="s">
+      <c r="E186" t="s">
         <v>1262</v>
       </c>
-      <c r="F185" t="s">
+      <c r="F186" t="s">
         <v>1263</v>
       </c>
-      <c r="G185" t="s">
+      <c r="G186" t="s">
         <v>1264</v>
       </c>
-      <c r="H185" t="s">
-        <v>15</v>
-      </c>
-      <c r="I185" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A186" t="s">
+      <c r="H186" t="s">
+        <v>15</v>
+      </c>
+      <c r="I186" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A187" t="s">
         <v>1265</v>
       </c>
-      <c r="B186" t="s">
+      <c r="B187" t="s">
         <v>1266</v>
       </c>
-      <c r="C186" t="s">
+      <c r="C187" t="s">
         <v>1267</v>
       </c>
-      <c r="D186" t="s">
+      <c r="D187" t="s">
         <v>1268</v>
       </c>
-      <c r="E186" t="s">
+      <c r="E187" t="s">
         <v>1269</v>
       </c>
-      <c r="F186" t="s">
+      <c r="F187" t="s">
         <v>1270</v>
       </c>
-      <c r="G186" t="s">
+      <c r="G187" t="s">
         <v>1271</v>
       </c>
-      <c r="H186" t="s">
-        <v>15</v>
-      </c>
-      <c r="I186" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A187" t="s">
+      <c r="H187" t="s">
+        <v>15</v>
+      </c>
+      <c r="I187" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A188" t="s">
         <v>1272</v>
       </c>
-      <c r="B187" t="s">
+      <c r="B188" t="s">
         <v>1273</v>
       </c>
-      <c r="C187" t="s">
+      <c r="C188" t="s">
         <v>1274</v>
       </c>
-      <c r="D187" t="s">
+      <c r="D188" t="s">
         <v>1275</v>
       </c>
-      <c r="E187" t="s">
+      <c r="E188" t="s">
         <v>1276</v>
       </c>
-      <c r="F187" t="s">
+      <c r="F188" t="s">
         <v>1277</v>
-      </c>
-      <c r="G187" t="s">
-        <v>1278</v>
-      </c>
-      <c r="H187" t="s">
-        <v>15</v>
-      </c>
-      <c r="I187" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A188" t="s">
-        <v>1279</v>
-      </c>
-      <c r="B188" t="s">
-        <v>1280</v>
-      </c>
-      <c r="C188" t="s">
-        <v>1281</v>
-      </c>
-      <c r="D188" t="s">
-        <v>1282</v>
-      </c>
-      <c r="E188" t="s">
-        <v>1283</v>
-      </c>
-      <c r="F188" t="s">
-        <v>1284</v>
       </c>
       <c r="G188" t="s">
         <v>1278</v>
       </c>
       <c r="H188" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I188" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>1285</v>
+        <v>1279</v>
       </c>
       <c r="B189" t="s">
-        <v>1286</v>
+        <v>1280</v>
       </c>
       <c r="C189" t="s">
-        <v>1287</v>
+        <v>1281</v>
       </c>
       <c r="D189" t="s">
-        <v>1288</v>
+        <v>1282</v>
       </c>
       <c r="E189" t="s">
-        <v>1289</v>
+        <v>1283</v>
       </c>
       <c r="F189" t="s">
-        <v>1290</v>
+        <v>1284</v>
       </c>
       <c r="G189" t="s">
-        <v>1291</v>
+        <v>1278</v>
       </c>
       <c r="H189" t="s">
         <v>16</v>
@@ -9940,27 +9958,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>1292</v>
+        <v>1285</v>
       </c>
       <c r="B190" t="s">
-        <v>1293</v>
+        <v>1286</v>
       </c>
       <c r="C190" t="s">
-        <v>1294</v>
+        <v>1287</v>
       </c>
       <c r="D190" t="s">
-        <v>1295</v>
+        <v>1288</v>
       </c>
       <c r="E190" t="s">
-        <v>1296</v>
+        <v>1289</v>
       </c>
       <c r="F190" t="s">
-        <v>1297</v>
+        <v>1290</v>
       </c>
       <c r="G190" t="s">
-        <v>1298</v>
+        <v>1291</v>
       </c>
       <c r="H190" t="s">
         <v>16</v>
@@ -9969,114 +9987,114 @@
         <v>15</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B191" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C191" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D191" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E191" t="s">
+        <v>1296</v>
+      </c>
+      <c r="F191" t="s">
+        <v>1297</v>
+      </c>
+      <c r="G191" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H191" t="s">
+        <v>16</v>
+      </c>
+      <c r="I191" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
         <v>1299</v>
       </c>
-      <c r="B191" t="s">
+      <c r="B192" t="s">
         <v>1300</v>
       </c>
-      <c r="C191" t="s">
+      <c r="C192" t="s">
         <v>1301</v>
       </c>
-      <c r="D191" t="s">
+      <c r="D192" t="s">
         <v>1302</v>
       </c>
-      <c r="E191" t="s">
+      <c r="E192" t="s">
         <v>1303</v>
       </c>
-      <c r="F191" t="s">
+      <c r="F192" t="s">
         <v>1304</v>
       </c>
-      <c r="G191" t="s">
+      <c r="G192" t="s">
         <v>1305</v>
       </c>
-      <c r="H191" t="s">
-        <v>15</v>
-      </c>
-      <c r="I191" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A192" t="s">
+      <c r="H192" t="s">
+        <v>15</v>
+      </c>
+      <c r="I192" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
         <v>1306</v>
       </c>
-      <c r="B192" t="s">
+      <c r="B193" t="s">
         <v>1307</v>
       </c>
-      <c r="C192" t="s">
+      <c r="C193" t="s">
         <v>1226</v>
       </c>
-      <c r="D192" t="s">
+      <c r="D193" t="s">
         <v>1308</v>
       </c>
-      <c r="E192" t="s">
+      <c r="E193" t="s">
         <v>1309</v>
       </c>
-      <c r="F192" t="s">
+      <c r="F193" t="s">
         <v>1310</v>
       </c>
-      <c r="G192" t="s">
+      <c r="G193" t="s">
         <v>1311</v>
       </c>
-      <c r="H192" t="s">
-        <v>15</v>
-      </c>
-      <c r="I192" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A193" t="s">
+      <c r="H193" t="s">
+        <v>15</v>
+      </c>
+      <c r="I193" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A194" t="s">
         <v>1312</v>
       </c>
-      <c r="B193" t="s">
+      <c r="B194" t="s">
         <v>1313</v>
       </c>
-      <c r="C193" t="s">
+      <c r="C194" t="s">
         <v>1314</v>
       </c>
-      <c r="D193" t="s">
+      <c r="D194" t="s">
         <v>1315</v>
       </c>
-      <c r="E193" t="s">
+      <c r="E194" t="s">
         <v>1316</v>
       </c>
-      <c r="F193" t="s">
+      <c r="F194" t="s">
         <v>1317</v>
       </c>
-      <c r="G193" t="s">
+      <c r="G194" t="s">
         <v>1318</v>
-      </c>
-      <c r="H193" t="s">
-        <v>16</v>
-      </c>
-      <c r="I193" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A194" t="s">
-        <v>1319</v>
-      </c>
-      <c r="B194" t="s">
-        <v>1320</v>
-      </c>
-      <c r="C194" t="s">
-        <v>1321</v>
-      </c>
-      <c r="D194" t="s">
-        <v>1322</v>
-      </c>
-      <c r="E194" t="s">
-        <v>1323</v>
-      </c>
-      <c r="F194" t="s">
-        <v>1324</v>
-      </c>
-      <c r="G194" t="s">
-        <v>1325</v>
       </c>
       <c r="H194" t="s">
         <v>16</v>
@@ -10085,24 +10103,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>1326</v>
+        <v>1319</v>
       </c>
       <c r="B195" t="s">
-        <v>1327</v>
+        <v>1320</v>
       </c>
       <c r="C195" t="s">
         <v>1321</v>
       </c>
       <c r="D195" t="s">
-        <v>1261</v>
+        <v>1322</v>
       </c>
       <c r="E195" t="s">
-        <v>1328</v>
+        <v>1323</v>
       </c>
       <c r="F195" t="s">
-        <v>1329</v>
+        <v>1324</v>
       </c>
       <c r="G195" t="s">
         <v>1325</v>
@@ -10114,90 +10132,119 @@
         <v>15</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B196" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C196" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D196" t="s">
+        <v>1261</v>
+      </c>
+      <c r="E196" t="s">
+        <v>1328</v>
+      </c>
+      <c r="F196" t="s">
+        <v>1329</v>
+      </c>
+      <c r="G196" t="s">
+        <v>1325</v>
+      </c>
+      <c r="H196" t="s">
+        <v>16</v>
+      </c>
+      <c r="I196" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A197" t="s">
         <v>1330</v>
       </c>
-      <c r="B196" t="s">
+      <c r="B197" t="s">
         <v>1331</v>
       </c>
-      <c r="C196" t="s">
+      <c r="C197" t="s">
         <v>1332</v>
       </c>
-      <c r="D196" t="s">
+      <c r="D197" t="s">
         <v>1333</v>
       </c>
-      <c r="E196" t="s">
+      <c r="E197" t="s">
         <v>1334</v>
       </c>
-      <c r="F196" t="s">
+      <c r="F197" t="s">
         <v>1335</v>
       </c>
-      <c r="G196" t="s">
+      <c r="G197" t="s">
         <v>1336</v>
       </c>
-      <c r="H196" t="s">
-        <v>15</v>
-      </c>
-      <c r="I196" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A197" t="s">
+      <c r="H197" t="s">
+        <v>15</v>
+      </c>
+      <c r="I197" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A198" t="s">
         <v>1337</v>
       </c>
-      <c r="B197" t="s">
+      <c r="B198" t="s">
         <v>1338</v>
       </c>
-      <c r="C197" t="s">
+      <c r="C198" t="s">
         <v>1339</v>
       </c>
-      <c r="D197" t="s">
+      <c r="D198" t="s">
         <v>1340</v>
       </c>
-      <c r="E197" t="s">
+      <c r="E198" t="s">
         <v>1341</v>
       </c>
-      <c r="F197" t="s">
+      <c r="F198" t="s">
         <v>1342</v>
       </c>
-      <c r="G197" t="s">
+      <c r="G198" t="s">
         <v>1343</v>
       </c>
-      <c r="H197" t="s">
-        <v>15</v>
-      </c>
-      <c r="I197" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A198" t="s">
+      <c r="H198" t="s">
+        <v>15</v>
+      </c>
+      <c r="I198" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" ht="14.4" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
         <v>1344</v>
       </c>
-      <c r="B198" t="s">
+      <c r="B199" t="s">
         <v>1345</v>
       </c>
-      <c r="C198" t="s">
+      <c r="C199" t="s">
         <v>1346</v>
       </c>
-      <c r="D198" t="s">
+      <c r="D199" t="s">
         <v>1347</v>
       </c>
-      <c r="E198" t="s">
+      <c r="E199" t="s">
         <v>1348</v>
       </c>
-      <c r="F198" t="s">
+      <c r="F199" t="s">
         <v>1349</v>
       </c>
-      <c r="G198" t="s">
+      <c r="G199" t="s">
         <v>1350</v>
       </c>
-      <c r="H198" t="s">
+      <c r="H199" t="s">
         <v>16</v>
       </c>
-      <c r="I198" t="s">
+      <c r="I199" t="s">
         <v>15</v>
       </c>
     </row>
@@ -10205,7 +10252,7 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F160 A161:F198 G1:I160 G161:I198" numberStoredAsText="1"/>
+    <ignoredError sqref="A162:I199 A1:I160" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>